--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251120_201549.xlsx
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
